--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/175.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/175.xlsx
@@ -426,13 +426,13 @@
         <v>-2.672541556545344</v>
       </c>
       <c r="E2">
-        <v>-9.336248254945394</v>
+        <v>-8.92808783568605</v>
       </c>
       <c r="F2">
-        <v>-3.633327670289102</v>
+        <v>-3.004681150126117</v>
       </c>
       <c r="G2">
-        <v>-12.98906561691149</v>
+        <v>-12.18002787693331</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.635690920497107</v>
       </c>
       <c r="E3">
-        <v>-9.54951673833663</v>
+        <v>-9.797812968177196</v>
       </c>
       <c r="F3">
-        <v>-3.565357387957313</v>
+        <v>-3.532326033678993</v>
       </c>
       <c r="G3">
-        <v>-12.92631753676014</v>
+        <v>-12.52098427256839</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.521563334397426</v>
       </c>
       <c r="E4">
-        <v>-10.36414392757645</v>
+        <v>-11.46349439157454</v>
       </c>
       <c r="F4">
-        <v>-3.703090707717167</v>
+        <v>-3.143467634319737</v>
       </c>
       <c r="G4">
-        <v>-12.82760037932461</v>
+        <v>-10.56614685817523</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.320153000574348</v>
       </c>
       <c r="E5">
-        <v>-11.06268821410365</v>
+        <v>-9.332811143173572</v>
       </c>
       <c r="F5">
-        <v>-3.592380953845415</v>
+        <v>-2.979832012459914</v>
       </c>
       <c r="G5">
-        <v>-12.31758766518111</v>
+        <v>-10.84592106169904</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.019085502970722</v>
       </c>
       <c r="E6">
-        <v>-12.2527621263714</v>
+        <v>-10.55500099310373</v>
       </c>
       <c r="F6">
-        <v>-3.496702152817098</v>
+        <v>-3.081924822445761</v>
       </c>
       <c r="G6">
-        <v>-11.60136106939641</v>
+        <v>-10.87574245591679</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.614931028642763</v>
       </c>
       <c r="E7">
-        <v>-11.57544732599216</v>
+        <v>-11.99861057963892</v>
       </c>
       <c r="F7">
-        <v>-3.707900422582357</v>
+        <v>-3.002496427815768</v>
       </c>
       <c r="G7">
-        <v>-11.34637292032512</v>
+        <v>-10.79461753747695</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.108015266221368</v>
       </c>
       <c r="E8">
-        <v>-13.45134051282556</v>
+        <v>-13.88285427254246</v>
       </c>
       <c r="F8">
-        <v>-3.518937383869868</v>
+        <v>-3.501676573097494</v>
       </c>
       <c r="G8">
-        <v>-11.27809622912319</v>
+        <v>-10.40237748089302</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.5064613727712806</v>
       </c>
       <c r="E9">
-        <v>-13.99701257380183</v>
+        <v>-13.2335707262707</v>
       </c>
       <c r="F9">
-        <v>-3.331945267169144</v>
+        <v>-3.167430688526252</v>
       </c>
       <c r="G9">
-        <v>-10.23580738208459</v>
+        <v>-9.035916704103448</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.171393467717448</v>
       </c>
       <c r="E10">
-        <v>-14.72717466585058</v>
+        <v>-13.68348367588077</v>
       </c>
       <c r="F10">
-        <v>-3.536694686446733</v>
+        <v>-3.30471423580612</v>
       </c>
       <c r="G10">
-        <v>-11.15763540858573</v>
+        <v>-9.565789380937035</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.8949228755793541</v>
       </c>
       <c r="E11">
-        <v>-15.12822538091788</v>
+        <v>-14.56653610737649</v>
       </c>
       <c r="F11">
-        <v>-3.464667741412547</v>
+        <v>-3.069085718589293</v>
       </c>
       <c r="G11">
-        <v>-10.27530550091364</v>
+        <v>-9.618129105912914</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.623891688407951</v>
       </c>
       <c r="E12">
-        <v>-14.53524888045749</v>
+        <v>-14.64981474437755</v>
       </c>
       <c r="F12">
-        <v>-3.366844602574725</v>
+        <v>-3.120961589555427</v>
       </c>
       <c r="G12">
-        <v>-9.09867802643695</v>
+        <v>-8.728045900587844</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.312539845940633</v>
       </c>
       <c r="E13">
-        <v>-15.79357142449485</v>
+        <v>-16.51348105139024</v>
       </c>
       <c r="F13">
-        <v>-3.076700968483684</v>
+        <v>-2.738833148483832</v>
       </c>
       <c r="G13">
-        <v>-9.146651141846529</v>
+        <v>-8.667409948490553</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.909371399326134</v>
       </c>
       <c r="E14">
-        <v>-17.27192346361689</v>
+        <v>-18.23802357993928</v>
       </c>
       <c r="F14">
-        <v>-2.936105892134631</v>
+        <v>-2.751395103805097</v>
       </c>
       <c r="G14">
-        <v>-9.423167768559694</v>
+        <v>-8.528449799479645</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.366007656890682</v>
       </c>
       <c r="E15">
-        <v>-18.01913978877853</v>
+        <v>-17.44387867863615</v>
       </c>
       <c r="F15">
-        <v>-3.084632959561162</v>
+        <v>-2.799661708989945</v>
       </c>
       <c r="G15">
-        <v>-8.737358465189814</v>
+        <v>-6.764766595069538</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.646327738952067</v>
       </c>
       <c r="E16">
-        <v>-19.17872801402665</v>
+        <v>-18.83186954740914</v>
       </c>
       <c r="F16">
-        <v>-2.515830726677846</v>
+        <v>-2.297298314818187</v>
       </c>
       <c r="G16">
-        <v>-8.334508110152521</v>
+        <v>-7.800361519027733</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.735094987127945</v>
       </c>
       <c r="E17">
-        <v>-19.56526949837338</v>
+        <v>-19.05992349843542</v>
       </c>
       <c r="F17">
-        <v>-2.761196659715752</v>
+        <v>-2.2885705115182</v>
       </c>
       <c r="G17">
-        <v>-8.199000860139073</v>
+        <v>-6.171503592249985</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.639037621180647</v>
       </c>
       <c r="E18">
-        <v>-20.52204548671397</v>
+        <v>-19.67307887907398</v>
       </c>
       <c r="F18">
-        <v>-2.668051788152139</v>
+        <v>-2.351331985094108</v>
       </c>
       <c r="G18">
-        <v>-7.696383904730304</v>
+        <v>-6.279490277195471</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.38585990546159</v>
       </c>
       <c r="E19">
-        <v>-21.94298553236676</v>
+        <v>-20.93614273539737</v>
       </c>
       <c r="F19">
-        <v>-1.974326040806001</v>
+        <v>-2.072648838860144</v>
       </c>
       <c r="G19">
-        <v>-6.770202510845022</v>
+        <v>-6.79564736385986</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.015366225433109</v>
       </c>
       <c r="E20">
-        <v>-22.45268339582609</v>
+        <v>-21.71174806411309</v>
       </c>
       <c r="F20">
-        <v>-1.813996405044658</v>
+        <v>-1.529576284132014</v>
       </c>
       <c r="G20">
-        <v>-6.831431050593842</v>
+        <v>-6.472508324317139</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.570392181304349</v>
       </c>
       <c r="E21">
-        <v>-22.13658232466868</v>
+        <v>-21.4784320262899</v>
       </c>
       <c r="F21">
-        <v>-1.268966389805045</v>
+        <v>-1.518601202138019</v>
       </c>
       <c r="G21">
-        <v>-7.634599193330885</v>
+        <v>-7.103296360824332</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.090885311564164</v>
       </c>
       <c r="E22">
-        <v>-23.46045452996706</v>
+        <v>-23.02887737161405</v>
       </c>
       <c r="F22">
-        <v>-1.133240417293011</v>
+        <v>-0.9089385647834068</v>
       </c>
       <c r="G22">
-        <v>-7.436645122810165</v>
+        <v>-7.455551648384943</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.61194957578193</v>
       </c>
       <c r="E23">
-        <v>-23.35871330443673</v>
+        <v>-22.43217393704536</v>
       </c>
       <c r="F23">
-        <v>-1.069553267609529</v>
+        <v>-0.9469055385471945</v>
       </c>
       <c r="G23">
-        <v>-7.944217964891223</v>
+        <v>-6.956397523610251</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.162510806218057</v>
       </c>
       <c r="E24">
-        <v>-22.83732744956361</v>
+        <v>-22.4961386324037</v>
       </c>
       <c r="F24">
-        <v>-1.205639533217326</v>
+        <v>-1.121179704893982</v>
       </c>
       <c r="G24">
-        <v>-7.690464649306087</v>
+        <v>-6.326897289317834</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.7660025755167627</v>
       </c>
       <c r="E25">
-        <v>-23.49591248144712</v>
+        <v>-24.48337340966369</v>
       </c>
       <c r="F25">
-        <v>-1.083196102218082</v>
+        <v>-0.9156202200406459</v>
       </c>
       <c r="G25">
-        <v>-8.135564186515559</v>
+        <v>-7.395124260656626</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.4416102244357959</v>
       </c>
       <c r="E26">
-        <v>-23.53974810984137</v>
+        <v>-23.74513251998525</v>
       </c>
       <c r="F26">
-        <v>-0.9104985151101147</v>
+        <v>-0.815303536238965</v>
       </c>
       <c r="G26">
-        <v>-8.357873940568698</v>
+        <v>-7.336027712235095</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.2026596080800464</v>
       </c>
       <c r="E27">
-        <v>-24.30942566608105</v>
+        <v>-23.74396870216528</v>
       </c>
       <c r="F27">
-        <v>-1.124313067047679</v>
+        <v>-0.8284435442193661</v>
       </c>
       <c r="G27">
-        <v>-8.437029084412671</v>
+        <v>-8.161376510085256</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.0560407459689999</v>
       </c>
       <c r="E28">
-        <v>-23.77741601118593</v>
+        <v>-22.63369555886069</v>
       </c>
       <c r="F28">
-        <v>-1.399128011583182</v>
+        <v>-0.6908503824330292</v>
       </c>
       <c r="G28">
-        <v>-8.532107952300541</v>
+        <v>-8.373857254432298</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.00511804637746644</v>
       </c>
       <c r="E29">
-        <v>-24.13425976299036</v>
+        <v>-22.337506187915</v>
       </c>
       <c r="F29">
-        <v>-1.438921790120429</v>
+        <v>-0.9346009354371877</v>
       </c>
       <c r="G29">
-        <v>-9.114161447924122</v>
+        <v>-8.021376849775017</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.04892549614160985</v>
       </c>
       <c r="E30">
-        <v>-23.33363008690825</v>
+        <v>-22.11845031474197</v>
       </c>
       <c r="F30">
-        <v>-1.233261739941463</v>
+        <v>-0.9529972633509323</v>
       </c>
       <c r="G30">
-        <v>-8.483082083409473</v>
+        <v>-8.365097550935387</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.1807575118115221</v>
       </c>
       <c r="E31">
-        <v>-23.55235085300472</v>
+        <v>-21.7872060265029</v>
       </c>
       <c r="F31">
-        <v>-1.294056250770395</v>
+        <v>-1.165784782002334</v>
       </c>
       <c r="G31">
-        <v>-8.594568014989969</v>
+        <v>-8.494996736805311</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.3880838887836589</v>
       </c>
       <c r="E32">
-        <v>-22.3016089744562</v>
+        <v>-21.00011648770372</v>
       </c>
       <c r="F32">
-        <v>-1.444771207919105</v>
+        <v>-1.049412487629928</v>
       </c>
       <c r="G32">
-        <v>-8.704243078160484</v>
+        <v>-8.022879837449846</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.6547856972558475</v>
       </c>
       <c r="E33">
-        <v>-21.84679621596984</v>
+        <v>-22.53219887092678</v>
       </c>
       <c r="F33">
-        <v>-1.449649813991616</v>
+        <v>-1.138761216114233</v>
       </c>
       <c r="G33">
-        <v>-8.113423257948913</v>
+        <v>-7.999176331388664</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.959679564719794</v>
       </c>
       <c r="E34">
-        <v>-22.87431602525826</v>
+        <v>-20.97039158431738</v>
       </c>
       <c r="F34">
-        <v>-1.373231252453917</v>
+        <v>-1.084792477780845</v>
       </c>
       <c r="G34">
-        <v>-8.578386068394012</v>
+        <v>-7.683661478222884</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.278326648225245</v>
       </c>
       <c r="E35">
-        <v>-21.09011538013217</v>
+        <v>-21.74630032079162</v>
       </c>
       <c r="F35">
-        <v>-1.363827206728037</v>
+        <v>-0.932353656743179</v>
       </c>
       <c r="G35">
-        <v>-7.64557034124803</v>
+        <v>-7.418910530356289</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.586079069935072</v>
       </c>
       <c r="E36">
-        <v>-21.01463024689831</v>
+        <v>-20.79201952162925</v>
       </c>
       <c r="F36">
-        <v>-1.503562330765006</v>
+        <v>-0.5306395246153438</v>
       </c>
       <c r="G36">
-        <v>-6.954295327192813</v>
+        <v>-6.759165152017092</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.862262046629586</v>
       </c>
       <c r="E37">
-        <v>-20.51396216061028</v>
+        <v>-19.26318858274371</v>
       </c>
       <c r="F37">
-        <v>-1.485800277070395</v>
+        <v>-0.8998409661521649</v>
       </c>
       <c r="G37">
-        <v>-7.28685948988584</v>
+        <v>-6.435652020828432</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.091111160260292</v>
       </c>
       <c r="E38">
-        <v>-19.83968596629018</v>
+        <v>-19.27450976776288</v>
       </c>
       <c r="F38">
-        <v>-1.345592416817667</v>
+        <v>-0.9453669682503451</v>
       </c>
       <c r="G38">
-        <v>-6.915326895650052</v>
+        <v>-7.196657055577318</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.264411577169196</v>
       </c>
       <c r="E39">
-        <v>-19.72949913673555</v>
+        <v>-19.41073079438761</v>
       </c>
       <c r="F39">
-        <v>-1.420781230712028</v>
+        <v>-0.5423827039783273</v>
       </c>
       <c r="G39">
-        <v>-6.266248095038387</v>
+        <v>-6.987794737504699</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.38245112442616</v>
       </c>
       <c r="E40">
-        <v>-19.47356337124404</v>
+        <v>-18.47865763175886</v>
       </c>
       <c r="F40">
-        <v>-1.52951531145427</v>
+        <v>-1.066858591994409</v>
       </c>
       <c r="G40">
-        <v>-6.638780474027034</v>
+        <v>-6.504670274231158</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.452468073202859</v>
       </c>
       <c r="E41">
-        <v>-18.88347603720055</v>
+        <v>-18.46759909823213</v>
       </c>
       <c r="F41">
-        <v>-1.413232496466086</v>
+        <v>-0.7062669676668745</v>
       </c>
       <c r="G41">
-        <v>-7.107666280936169</v>
+        <v>-6.626998242452768</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.485680905459446</v>
       </c>
       <c r="E42">
-        <v>-19.84138414404306</v>
+        <v>-19.65396419028761</v>
       </c>
       <c r="F42">
-        <v>-1.37647705772761</v>
+        <v>-0.9426841704295906</v>
       </c>
       <c r="G42">
-        <v>-6.726086180988694</v>
+        <v>-7.205857061630953</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.494990380283886</v>
       </c>
       <c r="E43">
-        <v>-18.72413262229265</v>
+        <v>-17.17559829299973</v>
       </c>
       <c r="F43">
-        <v>-1.380997746263231</v>
+        <v>-1.01465806131561</v>
       </c>
       <c r="G43">
-        <v>-6.801771873107511</v>
+        <v>-7.094841227517033</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.491780097968497</v>
       </c>
       <c r="E44">
-        <v>-18.07212746314228</v>
+        <v>-17.09750023026345</v>
       </c>
       <c r="F44">
-        <v>-1.062043334158515</v>
+        <v>-0.9410798763372504</v>
       </c>
       <c r="G44">
-        <v>-6.458127314494544</v>
+        <v>-6.581570936562889</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.482803515188816</v>
       </c>
       <c r="E45">
-        <v>-17.32366580762853</v>
+        <v>-16.29783964761898</v>
       </c>
       <c r="F45">
-        <v>-1.484891229874932</v>
+        <v>-1.135901835083907</v>
       </c>
       <c r="G45">
-        <v>-6.769821798108006</v>
+        <v>-6.433831220781833</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.468191451239195</v>
       </c>
       <c r="E46">
-        <v>-17.60244772448873</v>
+        <v>-16.48189041671273</v>
       </c>
       <c r="F46">
-        <v>-1.808096308656688</v>
+        <v>-1.023883940126002</v>
       </c>
       <c r="G46">
-        <v>-7.186626102593326</v>
+        <v>-6.12024310511991</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.442509617273083</v>
       </c>
       <c r="E47">
-        <v>-16.69219727810295</v>
+        <v>-16.93090219999527</v>
       </c>
       <c r="F47">
-        <v>-1.651006143345376</v>
+        <v>-1.394728476550092</v>
       </c>
       <c r="G47">
-        <v>-7.467304085049355</v>
+        <v>-6.462556824426089</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.394305921835849</v>
       </c>
       <c r="E48">
-        <v>-16.2291879816627</v>
+        <v>-16.05952417449132</v>
       </c>
       <c r="F48">
-        <v>-1.428144671365864</v>
+        <v>-1.285191456908722</v>
       </c>
       <c r="G48">
-        <v>-6.863202356134228</v>
+        <v>-7.098353716334199</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.309794823995864</v>
       </c>
       <c r="E49">
-        <v>-15.94219594142659</v>
+        <v>-14.74598141840443</v>
       </c>
       <c r="F49">
-        <v>-1.720872121657945</v>
+        <v>-1.354153139143575</v>
       </c>
       <c r="G49">
-        <v>-7.234678671095848</v>
+        <v>-6.947369665924659</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.17514187960982</v>
       </c>
       <c r="E50">
-        <v>-15.66206906778611</v>
+        <v>-14.60443490634668</v>
       </c>
       <c r="F50">
-        <v>-1.761425287181645</v>
+        <v>-1.622940498964916</v>
       </c>
       <c r="G50">
-        <v>-7.455886013484409</v>
+        <v>-7.618106055454237</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.980061932992117</v>
       </c>
       <c r="E51">
-        <v>-14.25825571083032</v>
+        <v>-14.57360505530246</v>
       </c>
       <c r="F51">
-        <v>-1.623061652467447</v>
+        <v>-1.72230458365846</v>
       </c>
       <c r="G51">
-        <v>-6.91587975675511</v>
+        <v>-7.06037513790768</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.717815212415118</v>
       </c>
       <c r="E52">
-        <v>-14.78637087807884</v>
+        <v>-14.98862158420942</v>
       </c>
       <c r="F52">
-        <v>-1.970727069113165</v>
+        <v>-1.319301314915457</v>
       </c>
       <c r="G52">
-        <v>-7.528029421876207</v>
+        <v>-7.108275421315395</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.389362563542387</v>
       </c>
       <c r="E53">
-        <v>-14.17599145200698</v>
+        <v>-13.50850796869839</v>
       </c>
       <c r="F53">
-        <v>-1.912586057545552</v>
+        <v>-1.09958429103105</v>
       </c>
       <c r="G53">
-        <v>-7.667307383258885</v>
+        <v>-6.880072896202353</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.001907342425075</v>
       </c>
       <c r="E54">
-        <v>-13.29945096613429</v>
+        <v>-13.76551698252972</v>
       </c>
       <c r="F54">
-        <v>-2.049329561108256</v>
+        <v>-1.471085273557089</v>
       </c>
       <c r="G54">
-        <v>-7.571112861524282</v>
+        <v>-7.566219875217239</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.5686316402907735</v>
       </c>
       <c r="E55">
-        <v>-13.94106780591107</v>
+        <v>-13.62310100346249</v>
       </c>
       <c r="F55">
-        <v>-1.773347425313073</v>
+        <v>-1.735208619457461</v>
       </c>
       <c r="G55">
-        <v>-8.27151173908573</v>
+        <v>-7.25374410285651</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.1050800146014969</v>
       </c>
       <c r="E56">
-        <v>-13.01010411941419</v>
+        <v>-13.68397727954761</v>
       </c>
       <c r="F56">
-        <v>-1.904197959164427</v>
+        <v>-1.278989664543861</v>
       </c>
       <c r="G56">
-        <v>-8.003715089323006</v>
+        <v>-7.242955034944026</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.3694553164379764</v>
       </c>
       <c r="E57">
-        <v>-12.66921418153879</v>
+        <v>-13.9020051891209</v>
       </c>
       <c r="F57">
-        <v>-1.933766540458639</v>
+        <v>-1.762646324442449</v>
       </c>
       <c r="G57">
-        <v>-8.183716071384259</v>
+        <v>-7.559287592858006</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.8353636948634067</v>
       </c>
       <c r="E58">
-        <v>-13.08852823227903</v>
+        <v>-12.66985722484788</v>
       </c>
       <c r="F58">
-        <v>-2.086427872177425</v>
+        <v>-1.685713058482232</v>
       </c>
       <c r="G58">
-        <v>-8.459895022452418</v>
+        <v>-8.199222666690204</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.274264355061873</v>
       </c>
       <c r="E59">
-        <v>-12.79497896167981</v>
+        <v>-11.3621607287049</v>
       </c>
       <c r="F59">
-        <v>-2.004193150665273</v>
+        <v>-1.834826097097475</v>
       </c>
       <c r="G59">
-        <v>-7.446305294693758</v>
+        <v>-7.721702957014649</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.672998275031114</v>
       </c>
       <c r="E60">
-        <v>-13.4373113003498</v>
+        <v>-11.6853398047363</v>
       </c>
       <c r="F60">
-        <v>-2.325208756018934</v>
+        <v>-1.663459614811434</v>
       </c>
       <c r="G60">
-        <v>-8.055985292842557</v>
+        <v>-7.890964529346507</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.020898373052795</v>
       </c>
       <c r="E61">
-        <v>-12.26373009041798</v>
+        <v>-11.59287742244769</v>
       </c>
       <c r="F61">
-        <v>-2.151894315456903</v>
+        <v>-1.526486473890992</v>
       </c>
       <c r="G61">
-        <v>-8.025375988786456</v>
+        <v>-7.344876800461567</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.311756644556668</v>
       </c>
       <c r="E62">
-        <v>-12.13063371085854</v>
+        <v>-13.03627417070452</v>
       </c>
       <c r="F62">
-        <v>-2.05734628045221</v>
+        <v>-1.515320555334186</v>
       </c>
       <c r="G62">
-        <v>-8.500336646760154</v>
+        <v>-7.538974085429038</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.542382765332239</v>
       </c>
       <c r="E63">
-        <v>-11.96244618621366</v>
+        <v>-11.99837057051651</v>
       </c>
       <c r="F63">
-        <v>-2.145740034269505</v>
+        <v>-1.910232670555209</v>
       </c>
       <c r="G63">
-        <v>-7.869359909157223</v>
+        <v>-8.29608591862374</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.713152737521314</v>
       </c>
       <c r="E64">
-        <v>-11.47180866985262</v>
+        <v>-10.70598937346747</v>
       </c>
       <c r="F64">
-        <v>-1.779772520212011</v>
+        <v>-1.580391863987762</v>
       </c>
       <c r="G64">
-        <v>-9.02836534972837</v>
+        <v>-7.399709366228516</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.825207232159173</v>
       </c>
       <c r="E65">
-        <v>-11.0836188209671</v>
+        <v>-10.40787992954253</v>
       </c>
       <c r="F65">
-        <v>-1.958393167443722</v>
+        <v>-1.76754235128003</v>
       </c>
       <c r="G65">
-        <v>-8.29213312724985</v>
+        <v>-8.042445161586938</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.881140405912172</v>
       </c>
       <c r="E66">
-        <v>-12.73352756939573</v>
+        <v>-11.39317171870942</v>
       </c>
       <c r="F66">
-        <v>-2.3834218262057</v>
+        <v>-2.090135327725468</v>
       </c>
       <c r="G66">
-        <v>-8.518471815224283</v>
+        <v>-9.283244250796859</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.884559034107191</v>
       </c>
       <c r="E67">
-        <v>-12.21864460319761</v>
+        <v>-10.34997886088046</v>
       </c>
       <c r="F67">
-        <v>-2.075278582532731</v>
+        <v>-1.737010876789231</v>
       </c>
       <c r="G67">
-        <v>-8.146409533702212</v>
+        <v>-7.988834187123981</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.841308282213427</v>
       </c>
       <c r="E68">
-        <v>-10.91101150569074</v>
+        <v>-10.58778714491926</v>
       </c>
       <c r="F68">
-        <v>-2.241252546176701</v>
+        <v>-2.062085520404163</v>
       </c>
       <c r="G68">
-        <v>-8.595941891388767</v>
+        <v>-7.812534394975633</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.759181957482825</v>
       </c>
       <c r="E69">
-        <v>-11.66465826394327</v>
+        <v>-10.81123563787974</v>
       </c>
       <c r="F69">
-        <v>-2.249110103076153</v>
+        <v>-2.186627361741363</v>
       </c>
       <c r="G69">
-        <v>-8.725900667078397</v>
+        <v>-8.315558547485733</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.647769158730964</v>
       </c>
       <c r="E70">
-        <v>-11.12431621687403</v>
+        <v>-10.06085843786074</v>
       </c>
       <c r="F70">
-        <v>-2.40162177458593</v>
+        <v>-2.080019406190599</v>
       </c>
       <c r="G70">
-        <v>-9.23540355720885</v>
+        <v>-7.713721231719467</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.516695988869288</v>
       </c>
       <c r="E71">
-        <v>-11.639113142066</v>
+        <v>-11.31347510464843</v>
       </c>
       <c r="F71">
-        <v>-2.330210099299892</v>
+        <v>-1.837869188013992</v>
       </c>
       <c r="G71">
-        <v>-9.00265565307039</v>
+        <v>-8.944827043590401</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.376486636725982</v>
       </c>
       <c r="E72">
-        <v>-12.25475465493478</v>
+        <v>-10.82685434473219</v>
       </c>
       <c r="F72">
-        <v>-2.409252861539475</v>
+        <v>-2.309775541872977</v>
       </c>
       <c r="G72">
-        <v>-8.85920640430823</v>
+        <v>-8.325212098278248</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.237073715692012</v>
       </c>
       <c r="E73">
-        <v>-10.74216282384074</v>
+        <v>-11.61386689947324</v>
       </c>
       <c r="F73">
-        <v>-2.393198042821707</v>
+        <v>-1.690577411201504</v>
       </c>
       <c r="G73">
-        <v>-8.581637024113576</v>
+        <v>-8.534749767640879</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.10757011135627</v>
       </c>
       <c r="E74">
-        <v>-12.02749318685984</v>
+        <v>-11.89801505803253</v>
       </c>
       <c r="F74">
-        <v>-2.404214301169504</v>
+        <v>-2.119557416222503</v>
       </c>
       <c r="G74">
-        <v>-8.806125117131556</v>
+        <v>-7.953143195665098</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.995383234108181</v>
       </c>
       <c r="E75">
-        <v>-12.11068578285475</v>
+        <v>-11.86359412710023</v>
       </c>
       <c r="F75">
-        <v>-2.556683212619564</v>
+        <v>-2.11801647036678</v>
       </c>
       <c r="G75">
-        <v>-8.115333442725072</v>
+        <v>-7.797719703687394</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.908123611149308</v>
       </c>
       <c r="E76">
-        <v>-13.1744741404706</v>
+        <v>-12.50706311274614</v>
       </c>
       <c r="F76">
-        <v>-2.760844285149567</v>
+        <v>-2.402753332462511</v>
       </c>
       <c r="G76">
-        <v>-8.294056554208167</v>
+        <v>-8.761197703618107</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.850466206163755</v>
       </c>
       <c r="E77">
-        <v>-13.08907617763396</v>
+        <v>-13.29431567660959</v>
       </c>
       <c r="F77">
-        <v>-2.905266386843279</v>
+        <v>-2.19706002445932</v>
       </c>
       <c r="G77">
-        <v>-8.695410542661708</v>
+        <v>-8.016887750023765</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.823460691268763</v>
       </c>
       <c r="E78">
-        <v>-13.40904003711991</v>
+        <v>-12.95597979807452</v>
       </c>
       <c r="F78">
-        <v>-2.58020124546384</v>
+        <v>-1.972703534095633</v>
       </c>
       <c r="G78">
-        <v>-8.800116476977779</v>
+        <v>-8.95768520246493</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.824180449743656</v>
       </c>
       <c r="E79">
-        <v>-13.49956876100725</v>
+        <v>-11.94930908311741</v>
       </c>
       <c r="F79">
-        <v>-2.721672903037088</v>
+        <v>-2.183204181405141</v>
       </c>
       <c r="G79">
-        <v>-8.89222909606246</v>
+        <v>-8.115906167103367</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.848477082243806</v>
       </c>
       <c r="E80">
-        <v>-14.17239131517088</v>
+        <v>-12.61241353206058</v>
       </c>
       <c r="F80">
-        <v>-2.664799648054784</v>
+        <v>-2.133774344225402</v>
       </c>
       <c r="G80">
-        <v>-8.975383378917874</v>
+        <v>-7.917395924932048</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.890652794549801</v>
       </c>
       <c r="E81">
-        <v>-14.98834081882094</v>
+        <v>-14.109291558348</v>
       </c>
       <c r="F81">
-        <v>-3.13196201084407</v>
+        <v>-2.584067863456385</v>
       </c>
       <c r="G81">
-        <v>-8.879096161908171</v>
+        <v>-8.412468147056819</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.945247363202893</v>
       </c>
       <c r="E82">
-        <v>-15.23765142683923</v>
+        <v>-14.84084389191711</v>
       </c>
       <c r="F82">
-        <v>-3.042602196418357</v>
+        <v>-2.614129769143257</v>
       </c>
       <c r="G82">
-        <v>-8.269485685215695</v>
+        <v>-7.93746445199111</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.008532499112468</v>
       </c>
       <c r="E83">
-        <v>-15.99138875457191</v>
+        <v>-16.03840337171955</v>
       </c>
       <c r="F83">
-        <v>-2.869655967481665</v>
+        <v>-2.931473552331971</v>
       </c>
       <c r="G83">
-        <v>-8.904858827294779</v>
+        <v>-8.148263439204204</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.079450545318213</v>
       </c>
       <c r="E84">
-        <v>-17.24871503432758</v>
+        <v>-16.90161203011365</v>
       </c>
       <c r="F84">
-        <v>-2.907847035632487</v>
+        <v>-2.765119499268296</v>
       </c>
       <c r="G84">
-        <v>-8.800659406446218</v>
+        <v>-8.096529544062012</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.157559395179512</v>
       </c>
       <c r="E85">
-        <v>-18.63681458647675</v>
+        <v>-17.65720603218949</v>
       </c>
       <c r="F85">
-        <v>-2.959429129151308</v>
+        <v>-2.770908736242184</v>
       </c>
       <c r="G85">
-        <v>-9.147048407311242</v>
+        <v>-8.189824027904214</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.243083759943017</v>
       </c>
       <c r="E86">
-        <v>-18.20877869479774</v>
+        <v>-18.28517857978115</v>
       </c>
       <c r="F86">
-        <v>-3.255512452278205</v>
+        <v>-2.527704561778853</v>
       </c>
       <c r="G86">
-        <v>-8.605532541816036</v>
+        <v>-7.725705406571628</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.340033814880182</v>
       </c>
       <c r="E87">
-        <v>-19.41051795610926</v>
+        <v>-19.56933153955825</v>
       </c>
       <c r="F87">
-        <v>-3.589960259353665</v>
+        <v>-2.927548337220554</v>
       </c>
       <c r="G87">
-        <v>-8.60537694617569</v>
+        <v>-7.833384210781963</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.454415957400164</v>
       </c>
       <c r="E88">
-        <v>-22.0234791578531</v>
+        <v>-20.53099375135312</v>
       </c>
       <c r="F88">
-        <v>-3.244177077188447</v>
+        <v>-2.928934079896564</v>
       </c>
       <c r="G88">
-        <v>-8.529042387131176</v>
+        <v>-7.496423643612784</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.592364195494363</v>
       </c>
       <c r="E89">
-        <v>-23.32591809567318</v>
+        <v>-22.49343966189513</v>
       </c>
       <c r="F89">
-        <v>-3.413768225143281</v>
+        <v>-3.244590424432377</v>
       </c>
       <c r="G89">
-        <v>-8.656594396213755</v>
+        <v>-7.911370732050575</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.758161661064835</v>
       </c>
       <c r="E90">
-        <v>-24.23601910241672</v>
+        <v>-23.49825370250909</v>
       </c>
       <c r="F90">
-        <v>-3.437600623611771</v>
+        <v>-2.997898929543247</v>
       </c>
       <c r="G90">
-        <v>-8.4796027000477</v>
+        <v>-8.378300006546</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.956805691829227</v>
       </c>
       <c r="E91">
-        <v>-25.23728281940867</v>
+        <v>-26.15343386742645</v>
       </c>
       <c r="F91">
-        <v>-3.21888846113071</v>
+        <v>-3.367606365120051</v>
       </c>
       <c r="G91">
-        <v>-8.626928597636345</v>
+        <v>-7.460315523415954</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.190212050169148</v>
       </c>
       <c r="E92">
-        <v>-27.84626349249977</v>
+        <v>-26.44549327007714</v>
       </c>
       <c r="F92">
-        <v>-3.238300736389209</v>
+        <v>-2.648736910807439</v>
       </c>
       <c r="G92">
-        <v>-8.666181736095483</v>
+        <v>-7.857918663773502</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.454876775971457</v>
       </c>
       <c r="E93">
-        <v>-29.65725006138123</v>
+        <v>-29.16861865900558</v>
       </c>
       <c r="F93">
-        <v>-3.463325550649212</v>
+        <v>-2.701971601449021</v>
       </c>
       <c r="G93">
-        <v>-9.544009301834171</v>
+        <v>-7.667714580360215</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.738444083289548</v>
       </c>
       <c r="E94">
-        <v>-31.89221274499383</v>
+        <v>-30.58961757482048</v>
       </c>
       <c r="F94">
-        <v>-3.258788347964292</v>
+        <v>-3.232866249540379</v>
       </c>
       <c r="G94">
-        <v>-8.857537889356436</v>
+        <v>-7.743728016487421</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.025194736999373</v>
       </c>
       <c r="E95">
-        <v>-34.17832001404905</v>
+        <v>-33.09095868498627</v>
       </c>
       <c r="F95">
-        <v>-3.185859482411263</v>
+        <v>-3.161832288115173</v>
       </c>
       <c r="G95">
-        <v>-9.473077553109746</v>
+        <v>-8.295228487329069</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.294623146899729</v>
       </c>
       <c r="E96">
-        <v>-36.16144067267307</v>
+        <v>-36.10871112132776</v>
       </c>
       <c r="F96">
-        <v>-3.010057039856076</v>
+        <v>-3.244223004659995</v>
       </c>
       <c r="G96">
-        <v>-8.943625315559645</v>
+        <v>-8.844732699210535</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.528857370510482</v>
       </c>
       <c r="E97">
-        <v>-38.54797138132239</v>
+        <v>-37.75351627954974</v>
       </c>
       <c r="F97">
-        <v>-3.190790350778983</v>
+        <v>-2.547574528046914</v>
       </c>
       <c r="G97">
-        <v>-9.560495818619742</v>
+        <v>-8.952573720152294</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.712208308493207</v>
       </c>
       <c r="E98">
-        <v>-41.72230259919009</v>
+        <v>-39.60078271794365</v>
       </c>
       <c r="F98">
-        <v>-2.79620843824133</v>
+        <v>-3.160440210615502</v>
       </c>
       <c r="G98">
-        <v>-10.16223050747429</v>
+        <v>-9.111297826032652</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.841035298085565</v>
       </c>
       <c r="E99">
-        <v>-43.15143239008577</v>
+        <v>-42.77815027763349</v>
       </c>
       <c r="F99">
-        <v>-2.957927775943471</v>
+        <v>-3.008602405972745</v>
       </c>
       <c r="G99">
-        <v>-10.30178324413673</v>
+        <v>-9.339235507502552</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.912478639699863</v>
       </c>
       <c r="E100">
-        <v>-46.61062726540597</v>
+        <v>-44.87411371581765</v>
       </c>
       <c r="F100">
-        <v>-2.77240692203819</v>
+        <v>-2.902190829955495</v>
       </c>
       <c r="G100">
-        <v>-10.60410226278297</v>
+        <v>-9.300518677420776</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.938539097628311</v>
       </c>
       <c r="E101">
-        <v>-48.55707520939738</v>
+        <v>-47.87919774612268</v>
       </c>
       <c r="F101">
-        <v>-3.256971837279283</v>
+        <v>-2.961496657223914</v>
       </c>
       <c r="G101">
-        <v>-11.24879790110064</v>
+        <v>-9.613222877423715</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.922956972337992</v>
       </c>
       <c r="E102">
-        <v>-51.11395578903024</v>
+        <v>-49.99293318054994</v>
       </c>
       <c r="F102">
-        <v>-2.874608215879244</v>
+        <v>-2.680855258625509</v>
       </c>
       <c r="G102">
-        <v>-10.60997848111518</v>
+        <v>-10.08435985529955</v>
       </c>
     </row>
   </sheetData>
